--- a/artfynd/A 4362-2022 artfynd.xlsx
+++ b/artfynd/A 4362-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133713469</v>
       </c>
       <c r="B2" t="n">
-        <v>58444</v>
+        <v>58451</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>133713366</v>
       </c>
       <c r="B3" t="n">
-        <v>57952</v>
+        <v>57959</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 4362-2022 artfynd.xlsx
+++ b/artfynd/A 4362-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133713469</v>
       </c>
       <c r="B2" t="n">
-        <v>58451</v>
+        <v>58461</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>133713366</v>
       </c>
       <c r="B3" t="n">
-        <v>57959</v>
+        <v>57969</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 4362-2022 artfynd.xlsx
+++ b/artfynd/A 4362-2022 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133713469</v>
+        <v>133713366</v>
       </c>
       <c r="B2" t="n">
-        <v>58461</v>
+        <v>57969</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103018</v>
+        <v>102977</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -712,23 +712,23 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Borgstena kyrka, Vg</t>
+          <t>Stomsberg, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>383193</v>
+        <v>383226</v>
       </c>
       <c r="R2" t="n">
-        <v>6417251</v>
+        <v>6417331</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133713366</v>
+        <v>133713469</v>
       </c>
       <c r="B3" t="n">
-        <v>57969</v>
+        <v>58461</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -805,21 +805,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102977</v>
+        <v>103018</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -831,23 +831,23 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stomsberg, Vg</t>
+          <t>Borgstena kyrka, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>383226</v>
+        <v>383193</v>
       </c>
       <c r="R3" t="n">
-        <v>6417331</v>
+        <v>6417251</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>

--- a/artfynd/A 4362-2022 artfynd.xlsx
+++ b/artfynd/A 4362-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133713366</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -910,8 +920,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133713469</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>